--- a/productosV2.xlsx
+++ b/productosV2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jairo\Documents\Chumazero_Ambato\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jairo\Documents\Chumazero_Ambato\ChumaBot\test chumazero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8BE5C1-31E3-40B4-8DA1-DA6B1EEA0E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2E56D0-739E-4F1E-B156-8C50C12122E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="368">
   <si>
     <t>name</t>
   </si>
@@ -1110,6 +1110,33 @@
   </si>
   <si>
     <t>Canelazo frutos rojos 500</t>
+  </si>
+  <si>
+    <t>Jarra de pitufo pequeña</t>
+  </si>
+  <si>
+    <t>Jarra de pitufo Grande</t>
+  </si>
+  <si>
+    <t>Jarra de paloma grande</t>
+  </si>
+  <si>
+    <t>Jarra de paloma pequeña</t>
+  </si>
+  <si>
+    <t>Smirnoff</t>
+  </si>
+  <si>
+    <t>J pitufo p</t>
+  </si>
+  <si>
+    <t>J pitufo g</t>
+  </si>
+  <si>
+    <t>J paloma p</t>
+  </si>
+  <si>
+    <t>J paloma g</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -1537,7 +1564,7 @@
         <v>180</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E60" si="0">D3</f>
+        <f t="shared" ref="E3:E61" si="0">D3</f>
         <v>Michelada Pilsener 1lt</v>
       </c>
     </row>
@@ -2261,7 +2288,7 @@
         <v>Espuela 750ml + Hielos</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>211</v>
       </c>
@@ -2356,35 +2383,35 @@
         <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="C49">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>250</v>
+        <v>363</v>
       </c>
       <c r="E49" t="str">
-        <f t="shared" si="0"/>
-        <v>Azteca miniatura 50ml</v>
+        <f xml:space="preserve"> D49 &amp; " + Hielos"</f>
+        <v>Smirnoff + Hielos</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C50">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D50" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E50" t="str">
         <f t="shared" si="0"/>
-        <v>Barbados Blue Berry</v>
+        <v>Azteca miniatura 50ml</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2392,17 +2419,17 @@
         <v>218</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51">
         <v>6.5</v>
       </c>
       <c r="D51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E51" t="str">
         <f t="shared" si="0"/>
-        <v>Barbados Cannabis</v>
+        <v>Barbados Blue Berry</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -2410,17 +2437,17 @@
         <v>218</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52">
         <v>6.5</v>
       </c>
       <c r="D52" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E52" t="str">
         <f t="shared" si="0"/>
-        <v>Barbadados Cotton Candy</v>
+        <v>Barbados Cannabis</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -2428,17 +2455,17 @@
         <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53">
         <v>6.5</v>
       </c>
       <c r="D53" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E53" t="str">
         <f t="shared" si="0"/>
-        <v>Barbados Mythological Drink</v>
+        <v>Barbadados Cotton Candy</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -2446,17 +2473,17 @@
         <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="C54">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D54" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="0"/>
-        <v>Barbados Blue Berry PARA LLEVAR</v>
+        <v>Barbados Mythological Drink</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2464,17 +2491,17 @@
         <v>218</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C55">
         <v>5.5</v>
       </c>
       <c r="D55" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E55" t="str">
         <f t="shared" si="0"/>
-        <v>Barbados Cannabis PARA LLEVAR</v>
+        <v>Barbados Blue Berry PARA LLEVAR</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2482,17 +2509,17 @@
         <v>218</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C56">
         <v>5.5</v>
       </c>
       <c r="D56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E56" t="str">
         <f t="shared" si="0"/>
-        <v>Barbadados Cotton Candy PARA LLEVAR</v>
+        <v>Barbados Cannabis PARA LLEVAR</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2500,17 +2527,17 @@
         <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57">
         <v>5.5</v>
       </c>
       <c r="D57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E57" t="str">
         <f t="shared" si="0"/>
-        <v>Barbados Mythological Drink PARA LLEVAR</v>
+        <v>Barbadados Cotton Candy PARA LLEVAR</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -2518,17 +2545,17 @@
         <v>218</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>263</v>
       </c>
       <c r="E58" t="str">
         <f t="shared" si="0"/>
-        <v>Vodka 40</v>
+        <v>Barbados Mythological Drink PARA LLEVAR</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -2536,53 +2563,53 @@
         <v>218</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E59" t="str">
         <f t="shared" si="0"/>
-        <v>Cartago Guarana</v>
+        <v>Vodka 40</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60">
-        <v>18</v>
+        <v>6.5</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E60" t="str">
         <f t="shared" si="0"/>
-        <v>Ron Abuelo</v>
+        <v>Cartago Guarana</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C61">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>225</v>
+        <v>52</v>
       </c>
       <c r="E61" t="str">
-        <f>D61  &amp; "+ Hielos"</f>
-        <v>Antioqueño Tapa azul 750ml+ Hielos</v>
+        <f t="shared" si="0"/>
+        <v>Ron Abuelo</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2590,17 +2617,17 @@
         <v>224</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E62" t="str">
-        <f t="shared" ref="E62:E65" si="2">D62  &amp; "+ Hielos"</f>
-        <v>Antioqueño Tapa azul 375ml+ Hielos</v>
+        <f>D62  &amp; "+ Hielos"</f>
+        <v>Antioqueño Tapa azul 750ml+ Hielos</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2608,17 +2635,17 @@
         <v>224</v>
       </c>
       <c r="B63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="2"/>
-        <v>Zhumir Coco Tropical 700ml+ Hielos</v>
+        <f t="shared" ref="E63:E66" si="2">D63  &amp; "+ Hielos"</f>
+        <v>Antioqueño Tapa azul 375ml+ Hielos</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2626,17 +2653,17 @@
         <v>224</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C64">
         <v>6.5</v>
       </c>
       <c r="D64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="2"/>
-        <v>Zhumir Naranjilla 700ml+ Hielos</v>
+        <v>Zhumir Coco Tropical 700ml+ Hielos</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2644,17 +2671,17 @@
         <v>224</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C65">
         <v>6.5</v>
       </c>
       <c r="D65" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E65" t="str">
         <f t="shared" si="2"/>
-        <v>Zhumir Pink+ Hielos</v>
+        <v>Zhumir Naranjilla 700ml+ Hielos</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -2662,17 +2689,17 @@
         <v>224</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="C66">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="E66" t="str">
-        <f>D66</f>
-        <v>Zhumir Coco Tropical 700ml PARA LLEVAR</v>
+        <f t="shared" si="2"/>
+        <v>Zhumir Pink+ Hielos</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2680,17 +2707,17 @@
         <v>224</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C67">
         <v>5.5</v>
       </c>
       <c r="D67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E67" t="str">
-        <f t="shared" ref="E67:E132" si="3">D67</f>
-        <v>Zhumir Naranjilla 700ml PARA LLEVAR</v>
+        <f>D67</f>
+        <v>Zhumir Coco Tropical 700ml PARA LLEVAR</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2698,17 +2725,17 @@
         <v>224</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C68">
         <v>5.5</v>
       </c>
       <c r="D68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E68" t="str">
-        <f t="shared" si="3"/>
-        <v>Zhumir Pink PARA LLEVAR</v>
+        <f t="shared" ref="E68:E133" si="3">D68</f>
+        <v>Zhumir Naranjilla 700ml PARA LLEVAR</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2716,17 +2743,17 @@
         <v>224</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="D69" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="E69" t="str">
-        <f>D69  &amp; " + Hielos"</f>
-        <v>Norteño 750ml + Hielos</v>
+        <f t="shared" si="3"/>
+        <v>Zhumir Pink PARA LLEVAR</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2734,17 +2761,17 @@
         <v>224</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E70" t="str">
-        <f t="shared" ref="E70:E71" si="4">D70  &amp; " + Hielos"</f>
-        <v>Norteño Black 750 ml + Hielos</v>
+        <f>D70  &amp; " + Hielos"</f>
+        <v>Norteño 750ml + Hielos</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2752,17 +2779,17 @@
         <v>224</v>
       </c>
       <c r="B71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C71">
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E71" t="str">
-        <f t="shared" si="4"/>
-        <v>Norteño Gold 750ml  + Hielos</v>
+        <f t="shared" ref="E71:E72" si="4">D71  &amp; " + Hielos"</f>
+        <v>Norteño Black 750 ml + Hielos</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2770,35 +2797,35 @@
         <v>224</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E72" t="str">
-        <f>D72  &amp; " + Hielos"</f>
-        <v>Norteño 375ml + Hielos</v>
+        <f t="shared" si="4"/>
+        <v>Norteño Gold 750ml  + Hielos</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C73">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">Fraile 1500ml </v>
+        <f>D73  &amp; " + Hielos"</f>
+        <v>Norteño 375ml + Hielos</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2806,17 +2833,17 @@
         <v>234</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C74">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="D74" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="3"/>
-        <v>Cavic Tinto 1000ml</v>
+        <v xml:space="preserve">Fraile 1500ml </v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2824,17 +2851,17 @@
         <v>234</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C75">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="D75" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E75" t="str">
         <f t="shared" si="3"/>
-        <v>Miraflores 750ml</v>
+        <v>Cavic Tinto 1000ml</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2842,17 +2869,17 @@
         <v>234</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="D76" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="3"/>
-        <v>Haciendazo 1500ml</v>
+        <v>Miraflores 750ml</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2860,17 +2887,17 @@
         <v>234</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="C77">
         <v>5.5</v>
       </c>
       <c r="D77" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="E77" t="str">
         <f t="shared" si="3"/>
-        <v>Fraile 1500ml PARA LLEVAR</v>
+        <v>Haciendazo 1500ml</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2878,17 +2905,17 @@
         <v>234</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D78" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E78" t="str">
         <f t="shared" si="3"/>
-        <v>Cavic Tinto 1000ml PARA LLEVAR</v>
+        <v>Fraile 1500ml PARA LLEVAR</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2896,17 +2923,17 @@
         <v>234</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C79">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="D79" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E79" t="str">
         <f t="shared" si="3"/>
-        <v>Miraflores 750ml PARA LLEVAR</v>
+        <v>Cavic Tinto 1000ml PARA LLEVAR</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2914,17 +2941,17 @@
         <v>234</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C80">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E80" t="str">
         <f t="shared" si="3"/>
-        <v>Haciendazo 1500ml PARA LLEVAR</v>
+        <v>Miraflores 750ml PARA LLEVAR</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2932,35 +2959,35 @@
         <v>234</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="C81">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="D81" t="s">
-        <v>66</v>
+        <v>259</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" si="3"/>
-        <v>Vino Caliente</v>
+        <v>Haciendazo 1500ml PARA LLEVAR</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82">
-        <v>19</v>
+        <v>7.5</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="E82" t="str">
-        <f>D82 &amp; " + Hielos"</f>
-        <v>Old Times Black 745ml + Hielos</v>
+        <f t="shared" si="3"/>
+        <v>Vino Caliente</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2968,17 +2995,17 @@
         <v>239</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C83">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E83" t="str">
-        <f t="shared" ref="E83:E88" si="5">D83 &amp; " + Hielos"</f>
-        <v>Old Time Red 745cc + Hielos</v>
+        <f>D83 &amp; " + Hielos"</f>
+        <v>Old Times Black 745ml + Hielos</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2986,17 +3013,17 @@
         <v>239</v>
       </c>
       <c r="B84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C84">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D84" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E84" t="str">
-        <f t="shared" si="5"/>
-        <v>Johnnie Walker Red 750 ml  + Hielos</v>
+        <f t="shared" ref="E84:E89" si="5">D84 &amp; " + Hielos"</f>
+        <v>Old Time Red 745cc + Hielos</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -3004,17 +3031,17 @@
         <v>239</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="5"/>
-        <v>Old Times Miel 750ml + Hielos</v>
+        <v>Johnnie Walker Red 750 ml  + Hielos</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -3022,17 +3049,17 @@
         <v>239</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C86">
         <v>10</v>
       </c>
       <c r="D86" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="5"/>
-        <v>Old Times Manzana 750ml + Hielos</v>
+        <v>Old Times Miel 750ml + Hielos</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3040,17 +3067,17 @@
         <v>239</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="5"/>
-        <v>Buchanans + Hielos</v>
+        <v>Old Times Manzana 750ml + Hielos</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -3058,17 +3085,17 @@
         <v>239</v>
       </c>
       <c r="B88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C88">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="D88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E88" t="str">
         <f t="shared" si="5"/>
-        <v>Something Special + Hielos</v>
+        <v>Buchanans + Hielos</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -3076,35 +3103,35 @@
         <v>239</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C89">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="E89" t="str">
-        <f t="shared" si="3"/>
-        <v>John Morris Petit</v>
+        <f t="shared" si="5"/>
+        <v>Something Special + Hielos</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C90">
-        <v>22</v>
+        <v>3.5</v>
       </c>
       <c r="D90" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E90" t="str">
-        <f>D90 &amp; " + Hielos"</f>
-        <v>Gluksmaister litro + Hielos</v>
+        <f t="shared" si="3"/>
+        <v>John Morris Petit</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -3112,17 +3139,17 @@
         <v>240</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C91">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D91" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E91" t="str">
         <f>D91 &amp; " + Hielos"</f>
-        <v>Jagermaister 1L + Hielos</v>
+        <v>Gluksmaister litro + Hielos</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -3130,35 +3157,35 @@
         <v>240</v>
       </c>
       <c r="B92" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C92">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D92" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E92" t="str">
-        <f t="shared" si="3"/>
-        <v>Jagermeister Miniatura</v>
+        <f>D92 &amp; " + Hielos"</f>
+        <v>Jagermaister 1L + Hielos</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C93">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D93" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="E93" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">Four Loko Blue </v>
+        <v>Jagermeister Miniatura</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -3166,17 +3193,17 @@
         <v>251</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C94">
         <v>5.5</v>
       </c>
       <c r="D94" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E94" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">Four loko Gold </v>
+        <v xml:space="preserve">Four Loko Blue </v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -3184,17 +3211,17 @@
         <v>251</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C95">
         <v>5.5</v>
       </c>
       <c r="D95" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E95" t="str">
         <f t="shared" si="3"/>
-        <v>Four Loko Red</v>
+        <v xml:space="preserve">Four loko Gold </v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3202,17 +3229,17 @@
         <v>251</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C96">
         <v>5.5</v>
       </c>
       <c r="D96" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="3"/>
-        <v>Four Loko Withe</v>
+        <v>Four Loko Red</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -3220,35 +3247,35 @@
         <v>251</v>
       </c>
       <c r="B97" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="D97" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" si="3"/>
-        <v>Jelly Four loko</v>
+        <v>Four Loko Withe</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C98">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E98" t="str">
         <f t="shared" si="3"/>
-        <v>Gelatina Switch</v>
+        <v>Jelly Four loko</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -3256,17 +3283,17 @@
         <v>252</v>
       </c>
       <c r="B99" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C99">
-        <v>4.5</v>
+        <v>0.25</v>
       </c>
       <c r="D99" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E99" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Bongo Bongo</v>
+        <v>Gelatina Switch</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -3274,17 +3301,17 @@
         <v>252</v>
       </c>
       <c r="B100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C100">
         <v>4.5</v>
       </c>
       <c r="D100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E100" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Daiquiri</v>
+        <v>Switch Bongo Bongo</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -3292,17 +3319,17 @@
         <v>252</v>
       </c>
       <c r="B101" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C101">
         <v>4.5</v>
       </c>
       <c r="D101" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E101" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Harta Demencia</v>
+        <v>Switch Daiquiri</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -3310,17 +3337,17 @@
         <v>252</v>
       </c>
       <c r="B102" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C102">
         <v>4.5</v>
       </c>
       <c r="D102" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E102" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Maracuya</v>
+        <v>Switch Harta Demencia</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -3328,17 +3355,17 @@
         <v>252</v>
       </c>
       <c r="B103" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C103">
         <v>4.5</v>
       </c>
       <c r="D103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E103" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Tamarindo</v>
+        <v>Switch Maracuya</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -3346,17 +3373,17 @@
         <v>252</v>
       </c>
       <c r="B104" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D104" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E104" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Bongo Bongo PARA LLEVAR</v>
+        <v>Switch Tamarindo</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -3364,17 +3391,17 @@
         <v>252</v>
       </c>
       <c r="B105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C105">
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E105" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Daiquiri PARA LLEVAR</v>
+        <v>Switch Bongo Bongo PARA LLEVAR</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -3382,17 +3409,17 @@
         <v>252</v>
       </c>
       <c r="B106" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E106" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Harta Demencia PARA LLEVAR</v>
+        <v>Switch Daiquiri PARA LLEVAR</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -3400,17 +3427,17 @@
         <v>252</v>
       </c>
       <c r="B107" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C107">
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E107" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Maracuya PARA LLEVAR</v>
+        <v>Switch Harta Demencia PARA LLEVAR</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -3418,35 +3445,35 @@
         <v>252</v>
       </c>
       <c r="B108" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E108" t="str">
         <f t="shared" si="3"/>
-        <v>Switch Tamarindo PARA LLEVAR</v>
+        <v>Switch Maracuya PARA LLEVAR</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B109" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C109">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>90</v>
+        <v>291</v>
       </c>
       <c r="E109" t="str">
         <f t="shared" si="3"/>
-        <v>RTD</v>
+        <v>Switch Tamarindo PARA LLEVAR</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -3454,35 +3481,35 @@
         <v>251</v>
       </c>
       <c r="B110" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="C110">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D110" t="s">
-        <v>292</v>
+        <v>90</v>
       </c>
       <c r="E110" t="str">
         <f t="shared" si="3"/>
-        <v>RTD PARA LLEVAR</v>
+        <v>RTD</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B111" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C111">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D111" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E111" t="str">
         <f t="shared" si="3"/>
-        <v>Cubata Berrylicious</v>
+        <v>RTD PARA LLEVAR</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -3490,17 +3517,17 @@
         <v>253</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C112">
         <v>4.5</v>
       </c>
       <c r="D112" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E112" t="str">
         <f t="shared" si="3"/>
-        <v>Cubata Guarana</v>
+        <v>Cubata Berrylicious</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3508,17 +3535,17 @@
         <v>253</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C113">
         <v>4.5</v>
       </c>
       <c r="D113" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E113" t="str">
         <f t="shared" si="3"/>
-        <v>Cubata Piña Paradice</v>
+        <v>Cubata Guarana</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3526,17 +3553,17 @@
         <v>253</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D114" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E114" t="str">
         <f t="shared" si="3"/>
-        <v>Cubata Berrylicious PARA LLEVAR</v>
+        <v>Cubata Piña Paradice</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3544,17 +3571,17 @@
         <v>253</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C115">
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E115" t="str">
         <f t="shared" si="3"/>
-        <v>Cubata Guarana PARA LLEVAR</v>
+        <v>Cubata Berrylicious PARA LLEVAR</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3562,35 +3589,35 @@
         <v>253</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E116" t="str">
         <f t="shared" si="3"/>
-        <v>Cubata Piña Paradice PARA LLEVAR</v>
+        <v>Cubata Guarana PARA LLEVAR</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="B117" t="s">
-        <v>354</v>
+        <v>126</v>
       </c>
       <c r="C117">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="D117" t="s">
-        <v>356</v>
+        <v>298</v>
       </c>
       <c r="E117" t="str">
         <f t="shared" si="3"/>
-        <v>Canelazo Amazonico</v>
+        <v>Cubata Piña Paradice PARA LLEVAR</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3598,17 +3625,17 @@
         <v>209</v>
       </c>
       <c r="B118" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C118">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D118" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E118" t="str">
         <f t="shared" si="3"/>
-        <v>Canelazo Frutos rojos</v>
+        <v>Canelazo Amazonico</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -3616,18 +3643,17 @@
         <v>209</v>
       </c>
       <c r="B119" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C119">
-        <v>3</v>
-      </c>
-      <c r="D119" t="str">
-        <f>B119</f>
-        <v>Canelazo amazonico 500</v>
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>355</v>
       </c>
       <c r="E119" t="str">
         <f t="shared" si="3"/>
-        <v>Canelazo amazonico 500</v>
+        <v>Canelazo Frutos rojos</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3635,37 +3661,37 @@
         <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C120">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D120" t="str">
         <f>B120</f>
-        <v>Canelazo frutos rojos 500</v>
+        <v>Canelazo amazonico 500</v>
       </c>
       <c r="E120" t="str">
         <f t="shared" si="3"/>
-        <v>Canelazo frutos rojos 500</v>
+        <v>Canelazo amazonico 500</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>94</v>
+        <v>358</v>
       </c>
       <c r="C121">
         <v>3.5</v>
       </c>
       <c r="D121" t="str">
         <f>B121</f>
-        <v>Monster</v>
+        <v>Canelazo frutos rojos 500</v>
       </c>
       <c r="E121" t="str">
         <f t="shared" si="3"/>
-        <v>Monster</v>
+        <v>Canelazo frutos rojos 500</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3673,18 +3699,18 @@
         <v>254</v>
       </c>
       <c r="B122" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D122" t="str">
-        <f t="shared" ref="D122:D158" si="6">B122</f>
-        <v>Redbull</v>
+        <f>B122</f>
+        <v>Monster</v>
       </c>
       <c r="E122" t="str">
         <f t="shared" si="3"/>
-        <v>Redbull</v>
+        <v>Monster</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3692,18 +3718,18 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C123">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D123" t="str">
-        <f t="shared" si="6"/>
-        <v>Gatorade G</v>
+        <f t="shared" ref="D123:D159" si="6">B123</f>
+        <v>Redbull</v>
       </c>
       <c r="E123" t="str">
         <f t="shared" si="3"/>
-        <v>Gatorade G</v>
+        <v>Redbull</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3711,18 +3737,18 @@
         <v>254</v>
       </c>
       <c r="B124" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D124" t="str">
         <f t="shared" si="6"/>
-        <v>Gatorade P</v>
+        <v>Gatorade G</v>
       </c>
       <c r="E124" t="str">
         <f t="shared" si="3"/>
-        <v>Gatorade P</v>
+        <v>Gatorade G</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3730,18 +3756,18 @@
         <v>254</v>
       </c>
       <c r="B125" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C125">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D125" t="str">
         <f t="shared" si="6"/>
-        <v>Vive 100</v>
+        <v>Gatorade P</v>
       </c>
       <c r="E125" t="str">
         <f t="shared" si="3"/>
-        <v>Vive 100</v>
+        <v>Gatorade P</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3749,18 +3775,18 @@
         <v>254</v>
       </c>
       <c r="B126" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C126">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="D126" t="str">
         <f t="shared" si="6"/>
-        <v>Agua G</v>
+        <v>Vive 100</v>
       </c>
       <c r="E126" t="str">
         <f t="shared" si="3"/>
-        <v>Agua G</v>
+        <v>Vive 100</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3768,18 +3794,18 @@
         <v>254</v>
       </c>
       <c r="B127" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C127">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D127" t="str">
         <f t="shared" si="6"/>
-        <v>Agua P</v>
+        <v>Agua G</v>
       </c>
       <c r="E127" t="str">
         <f t="shared" si="3"/>
-        <v>Agua P</v>
+        <v>Agua G</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3787,18 +3813,18 @@
         <v>254</v>
       </c>
       <c r="B128" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C128">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="D128" t="str">
         <f t="shared" si="6"/>
-        <v>Sprite 1</v>
+        <v>Agua P</v>
       </c>
       <c r="E128" t="str">
         <f t="shared" si="3"/>
-        <v>Sprite 1</v>
+        <v>Agua P</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3806,18 +3832,18 @@
         <v>254</v>
       </c>
       <c r="B129" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C129">
         <v>1.75</v>
       </c>
       <c r="D129" t="str">
         <f t="shared" si="6"/>
-        <v>Coca Cola 1</v>
+        <v>Sprite 1</v>
       </c>
       <c r="E129" t="str">
         <f t="shared" si="3"/>
-        <v>Coca Cola 1</v>
+        <v>Sprite 1</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3825,18 +3851,18 @@
         <v>254</v>
       </c>
       <c r="B130" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C130">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="D130" t="str">
         <f t="shared" si="6"/>
-        <v>Coca Cola 1,5</v>
+        <v>Coca Cola 1</v>
       </c>
       <c r="E130" t="str">
         <f t="shared" si="3"/>
-        <v>Coca Cola 1,5</v>
+        <v>Coca Cola 1</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3844,37 +3870,37 @@
         <v>254</v>
       </c>
       <c r="B131" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C131">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="D131" t="str">
         <f t="shared" si="6"/>
-        <v>Cifrut</v>
+        <v>Coca Cola 1,5</v>
       </c>
       <c r="E131" t="str">
         <f t="shared" si="3"/>
-        <v>Cifrut</v>
+        <v>Coca Cola 1,5</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B132" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C132">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D132" t="str">
         <f t="shared" si="6"/>
-        <v>Lark</v>
+        <v>Cifrut</v>
       </c>
       <c r="E132" t="str">
         <f t="shared" si="3"/>
-        <v>Lark</v>
+        <v>Cifrut</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3882,18 +3908,18 @@
         <v>255</v>
       </c>
       <c r="B133" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C133">
         <v>0.5</v>
       </c>
       <c r="D133" t="str">
         <f t="shared" si="6"/>
-        <v>Marlboro</v>
+        <v>Lark</v>
       </c>
       <c r="E133" t="str">
-        <f t="shared" ref="E133:E158" si="7">D133</f>
-        <v>Marlboro</v>
+        <f t="shared" si="3"/>
+        <v>Lark</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3901,18 +3927,18 @@
         <v>255</v>
       </c>
       <c r="B134" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C134">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D134" t="str">
-        <f>B134</f>
-        <v>Carnival</v>
+        <f t="shared" si="6"/>
+        <v>Marlboro</v>
       </c>
       <c r="E134" t="str">
-        <f t="shared" si="7"/>
-        <v>Carnival</v>
+        <f t="shared" ref="E134:E159" si="7">D134</f>
+        <v>Marlboro</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3920,18 +3946,18 @@
         <v>255</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C135">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
       <c r="D135" t="str">
-        <f t="shared" si="6"/>
-        <v>Media Lark</v>
+        <f>B135</f>
+        <v>Carnival</v>
       </c>
       <c r="E135" t="str">
         <f t="shared" si="7"/>
-        <v>Media Lark</v>
+        <v>Carnival</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3939,37 +3965,37 @@
         <v>255</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C136">
         <v>4.5</v>
       </c>
       <c r="D136" t="str">
         <f t="shared" si="6"/>
-        <v>Media Marlboro</v>
+        <v>Media Lark</v>
       </c>
       <c r="E136" t="str">
         <f t="shared" si="7"/>
-        <v>Media Marlboro</v>
+        <v>Media Lark</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B137" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C137">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D137" t="str">
         <f t="shared" si="6"/>
-        <v>Picadita de Carne</v>
+        <v>Media Marlboro</v>
       </c>
       <c r="E137" t="str">
         <f t="shared" si="7"/>
-        <v>Picadita de Carne</v>
+        <v>Media Marlboro</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3977,18 +4003,18 @@
         <v>267</v>
       </c>
       <c r="B138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C138">
         <v>2.5</v>
       </c>
       <c r="D138" t="str">
         <f t="shared" si="6"/>
-        <v>Picadita de Pollo</v>
+        <v>Picadita de Carne</v>
       </c>
       <c r="E138" t="str">
         <f t="shared" si="7"/>
-        <v>Picadita de Pollo</v>
+        <v>Picadita de Carne</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3996,18 +4022,18 @@
         <v>267</v>
       </c>
       <c r="B139" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C139">
         <v>2.5</v>
       </c>
       <c r="D139" t="str">
         <f t="shared" si="6"/>
-        <v>Doriloco de Carne</v>
+        <v>Picadita de Pollo</v>
       </c>
       <c r="E139" t="str">
         <f t="shared" si="7"/>
-        <v>Doriloco de Carne</v>
+        <v>Picadita de Pollo</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -4015,18 +4041,18 @@
         <v>267</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C140">
         <v>2.5</v>
       </c>
       <c r="D140" t="str">
         <f t="shared" si="6"/>
-        <v>Doriloco de Pollo</v>
+        <v>Doriloco de Carne</v>
       </c>
       <c r="E140" t="str">
         <f t="shared" si="7"/>
-        <v>Doriloco de Pollo</v>
+        <v>Doriloco de Carne</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -4034,18 +4060,18 @@
         <v>267</v>
       </c>
       <c r="B141" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C141">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D141" t="str">
-        <f>B141</f>
-        <v>Hielos</v>
+        <f t="shared" si="6"/>
+        <v>Doriloco de Pollo</v>
       </c>
       <c r="E141" t="str">
         <f t="shared" si="7"/>
-        <v>Hielos</v>
+        <v>Doriloco de Pollo</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -4053,18 +4079,18 @@
         <v>267</v>
       </c>
       <c r="B142" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C142">
         <v>0.5</v>
       </c>
       <c r="D142" t="str">
-        <f t="shared" si="6"/>
-        <v>Limon</v>
+        <f>B142</f>
+        <v>Hielos</v>
       </c>
       <c r="E142" t="str">
         <f t="shared" si="7"/>
-        <v>Limon</v>
+        <v>Hielos</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -4072,18 +4098,18 @@
         <v>267</v>
       </c>
       <c r="B143" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D143" t="str">
         <f t="shared" si="6"/>
-        <v>Chamoyada</v>
+        <v>Limon</v>
       </c>
       <c r="E143" t="str">
         <f t="shared" si="7"/>
-        <v>Chamoyada</v>
+        <v>Limon</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4091,37 +4117,37 @@
         <v>267</v>
       </c>
       <c r="B144" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144" t="str">
         <f t="shared" si="6"/>
-        <v>Canguil</v>
+        <v>Chamoyada</v>
       </c>
       <c r="E144" t="str">
         <f t="shared" si="7"/>
-        <v>Canguil</v>
+        <v>Chamoyada</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B145" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C145">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D145" t="str">
         <f t="shared" si="6"/>
-        <v>Shot de Tequila</v>
+        <v>Canguil</v>
       </c>
       <c r="E145" t="str">
         <f t="shared" si="7"/>
-        <v>Shot de Tequila</v>
+        <v>Canguil</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -4129,18 +4155,18 @@
         <v>268</v>
       </c>
       <c r="B146" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="C146">
         <v>1.5</v>
       </c>
       <c r="D146" t="str">
         <f t="shared" si="6"/>
-        <v>Shot de Whisky</v>
+        <v>Shot de Tequila</v>
       </c>
       <c r="E146" t="str">
         <f t="shared" si="7"/>
-        <v>Shot de Whisky</v>
+        <v>Shot de Tequila</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -4148,18 +4174,18 @@
         <v>268</v>
       </c>
       <c r="B147" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C147">
         <v>1.5</v>
       </c>
       <c r="D147" t="str">
         <f t="shared" si="6"/>
-        <v>Shot de Hierbas</v>
+        <v>Shot de Whisky</v>
       </c>
       <c r="E147" t="str">
         <f t="shared" si="7"/>
-        <v>Shot de Hierbas</v>
+        <v>Shot de Whisky</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -4167,18 +4193,18 @@
         <v>268</v>
       </c>
       <c r="B148" t="s">
-        <v>137</v>
+        <v>271</v>
       </c>
       <c r="C148">
         <v>1.5</v>
       </c>
       <c r="D148" t="str">
-        <f>B148</f>
-        <v>Shot de Vodka</v>
+        <f t="shared" si="6"/>
+        <v>Shot de Hierbas</v>
       </c>
       <c r="E148" t="str">
         <f t="shared" si="7"/>
-        <v>Shot de Vodka</v>
+        <v>Shot de Hierbas</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -4186,36 +4212,37 @@
         <v>268</v>
       </c>
       <c r="B149" t="s">
+        <v>137</v>
+      </c>
+      <c r="C149">
+        <v>1.5</v>
+      </c>
+      <c r="D149" t="str">
+        <f>B149</f>
+        <v>Shot de Vodka</v>
+      </c>
+      <c r="E149" t="str">
+        <f t="shared" si="7"/>
+        <v>Shot de Vodka</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>268</v>
+      </c>
+      <c r="B150" t="s">
         <v>269</v>
       </c>
-      <c r="C149">
+      <c r="C150">
         <v>0.75</v>
       </c>
-      <c r="D149" t="str">
+      <c r="D150" t="str">
         <f t="shared" si="6"/>
         <v>Shot Canelazo</v>
       </c>
-      <c r="E149" t="str">
+      <c r="E150" t="str">
         <f t="shared" si="7"/>
         <v>Shot Canelazo</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>254</v>
-      </c>
-      <c r="B150" t="s">
-        <v>138</v>
-      </c>
-      <c r="C150">
-        <v>1.5</v>
-      </c>
-      <c r="D150" t="s">
-        <v>299</v>
-      </c>
-      <c r="E150" t="str">
-        <f t="shared" si="7"/>
-        <v>V220 grande</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -4223,36 +4250,35 @@
         <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D151" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E151" t="str">
         <f t="shared" si="7"/>
-        <v>V220 pequeño</v>
+        <v>V220 grande</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B152" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C152">
-        <v>0.1</v>
-      </c>
-      <c r="D152" t="str">
-        <f t="shared" si="6"/>
-        <v>Menta</v>
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>300</v>
       </c>
       <c r="E152" t="str">
         <f t="shared" si="7"/>
-        <v>Menta</v>
+        <v>V220 pequeño</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -4260,18 +4286,18 @@
         <v>272</v>
       </c>
       <c r="B153" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C153">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D153" t="str">
         <f t="shared" si="6"/>
-        <v>Trident</v>
+        <v>Menta</v>
       </c>
       <c r="E153" t="str">
         <f t="shared" si="7"/>
-        <v>Trident</v>
+        <v>Menta</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -4279,18 +4305,18 @@
         <v>272</v>
       </c>
       <c r="B154" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C154">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="D154" t="str">
         <f t="shared" si="6"/>
-        <v>Trident Pack</v>
+        <v>Trident</v>
       </c>
       <c r="E154" t="str">
         <f t="shared" si="7"/>
-        <v>Trident Pack</v>
+        <v>Trident</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -4298,92 +4324,94 @@
         <v>272</v>
       </c>
       <c r="B155" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C155">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D155" t="str">
         <f t="shared" si="6"/>
-        <v>Chupete</v>
+        <v>Trident Pack</v>
       </c>
       <c r="E155" t="str">
         <f t="shared" si="7"/>
-        <v>Chupete</v>
+        <v>Trident Pack</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B156" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C156">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="D156" t="str">
         <f t="shared" si="6"/>
-        <v>Guitig</v>
+        <v>Chupete</v>
       </c>
       <c r="E156" t="str">
         <f t="shared" si="7"/>
-        <v>Guitig</v>
+        <v>Chupete</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B157" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C157">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="D157" t="str">
         <f t="shared" si="6"/>
-        <v>Coco Loko</v>
+        <v>Guitig</v>
       </c>
       <c r="E157" t="str">
         <f t="shared" si="7"/>
-        <v>Coco Loko</v>
+        <v>Guitig</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="B158" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C158">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="D158" t="str">
         <f t="shared" si="6"/>
-        <v>Manicho</v>
+        <v>Coco Loko</v>
       </c>
       <c r="E158" t="str">
         <f t="shared" si="7"/>
-        <v>Manicho</v>
+        <v>Coco Loko</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B159" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C159">
-        <v>8.5</v>
-      </c>
-      <c r="D159" t="s">
-        <v>312</v>
-      </c>
-      <c r="E159" t="s">
-        <v>330</v>
+        <v>0.75</v>
+      </c>
+      <c r="D159" t="str">
+        <f t="shared" si="6"/>
+        <v>Manicho</v>
+      </c>
+      <c r="E159" t="str">
+        <f t="shared" si="7"/>
+        <v>Manicho</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -4391,16 +4419,16 @@
         <v>274</v>
       </c>
       <c r="B160" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C160">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E160" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -4408,16 +4436,16 @@
         <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C161">
         <v>9</v>
       </c>
       <c r="D161" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E161" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -4425,16 +4453,16 @@
         <v>274</v>
       </c>
       <c r="B162" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C162">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D162" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E162" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -4442,16 +4470,16 @@
         <v>274</v>
       </c>
       <c r="B163" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C163">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E163" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -4459,16 +4487,16 @@
         <v>274</v>
       </c>
       <c r="B164" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C164">
         <v>10</v>
       </c>
       <c r="D164" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E164" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -4476,16 +4504,16 @@
         <v>274</v>
       </c>
       <c r="B165" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C165">
         <v>10</v>
       </c>
       <c r="D165" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="E165" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -4493,16 +4521,16 @@
         <v>274</v>
       </c>
       <c r="B166" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C166">
         <v>10</v>
       </c>
       <c r="D166" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E166" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -4510,16 +4538,16 @@
         <v>274</v>
       </c>
       <c r="B167" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C167">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D167" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E167" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -4527,16 +4555,16 @@
         <v>274</v>
       </c>
       <c r="B168" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C168">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="D168" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E168" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -4544,16 +4572,16 @@
         <v>274</v>
       </c>
       <c r="B169" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C169">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="D169" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E169" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -4561,16 +4589,16 @@
         <v>274</v>
       </c>
       <c r="B170" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C170">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D170" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E170" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -4578,16 +4606,16 @@
         <v>274</v>
       </c>
       <c r="B171" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C171">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E171" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -4595,16 +4623,16 @@
         <v>274</v>
       </c>
       <c r="B172" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C172">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E172" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
@@ -4612,16 +4640,16 @@
         <v>274</v>
       </c>
       <c r="B173" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C173">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E173" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
@@ -4629,16 +4657,16 @@
         <v>274</v>
       </c>
       <c r="B174" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C174">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D174" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E174" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
@@ -4646,16 +4674,16 @@
         <v>274</v>
       </c>
       <c r="B175" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C175">
         <v>12</v>
       </c>
       <c r="D175" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E175" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
@@ -4663,16 +4691,16 @@
         <v>274</v>
       </c>
       <c r="B176" t="s">
-        <v>321</v>
+        <v>168</v>
       </c>
       <c r="C176">
         <v>12</v>
       </c>
       <c r="D176" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="E176" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
@@ -4680,16 +4708,16 @@
         <v>274</v>
       </c>
       <c r="B177" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C177">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D177" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E177" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
@@ -4697,16 +4725,16 @@
         <v>274</v>
       </c>
       <c r="B178" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C178">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D178" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E178" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
@@ -4714,16 +4742,16 @@
         <v>274</v>
       </c>
       <c r="B179" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C179">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D179" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E179" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -4731,16 +4759,16 @@
         <v>274</v>
       </c>
       <c r="B180" t="s">
-        <v>169</v>
+        <v>324</v>
       </c>
       <c r="C180">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D180" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E180" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
@@ -4748,16 +4776,16 @@
         <v>274</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C181">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D181" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E181" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
@@ -4765,34 +4793,33 @@
         <v>274</v>
       </c>
       <c r="B182" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C182">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="D182" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E182" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B183" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C183">
-        <v>1.25</v>
+        <v>11.5</v>
       </c>
       <c r="D183" t="s">
-        <v>172</v>
-      </c>
-      <c r="E183" t="str">
-        <f>D183</f>
-        <v>Dorito</v>
+        <v>320</v>
+      </c>
+      <c r="E183" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
@@ -4800,42 +4827,128 @@
         <v>275</v>
       </c>
       <c r="B184" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="C184">
         <v>1.25</v>
       </c>
       <c r="D184" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="E184" t="str">
-        <f t="shared" ref="E184:E185" si="8">D184</f>
-        <v>Snacks</v>
+        <f>D184</f>
+        <v>Dorito</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>275</v>
+      </c>
+      <c r="B185" t="s">
+        <v>275</v>
+      </c>
+      <c r="C185">
+        <v>1.25</v>
+      </c>
+      <c r="D185" t="s">
+        <v>275</v>
+      </c>
+      <c r="E185" t="str">
+        <f t="shared" ref="E185:E186" si="8">D185</f>
+        <v>Snacks</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>267</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B186" t="s">
         <v>329</v>
       </c>
-      <c r="C185">
+      <c r="C186">
         <v>1.75</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D186" t="s">
         <v>329</v>
       </c>
-      <c r="E185" t="str">
+      <c r="E186" t="str">
         <f t="shared" si="8"/>
         <v>Hot dog</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>209</v>
+      </c>
+      <c r="B187" t="s">
+        <v>364</v>
+      </c>
+      <c r="C187">
+        <v>12</v>
+      </c>
+      <c r="D187" t="s">
+        <v>359</v>
+      </c>
+      <c r="E187" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>209</v>
+      </c>
+      <c r="B188" t="s">
+        <v>365</v>
+      </c>
+      <c r="C188">
+        <v>18</v>
+      </c>
+      <c r="D188" t="s">
+        <v>360</v>
+      </c>
+      <c r="E188" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>209</v>
+      </c>
+      <c r="B189" t="s">
+        <v>366</v>
+      </c>
+      <c r="C189">
+        <v>12</v>
+      </c>
+      <c r="D189" t="s">
+        <v>362</v>
+      </c>
+      <c r="E189" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>209</v>
+      </c>
+      <c r="B190" t="s">
+        <v>367</v>
+      </c>
+      <c r="C190">
+        <v>18</v>
+      </c>
+      <c r="D190" t="s">
+        <v>361</v>
+      </c>
+      <c r="E190" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError sqref="E43 E61 E69 E82 E89" formula="1"/>
+    <ignoredError sqref="E43 E62 E70 E83 E90" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>